--- a/delays_zurich_transport_40753.xlsx
+++ b/delays_zurich_transport_40753.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.334110000000001</v>
+        <v>9.288106000000001</v>
       </c>
       <c r="E2" t="n">
         <v>0.999894722</v>
       </c>
       <c r="F2" t="n">
-        <v>0.706124</v>
+        <v>0.8115250000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0.9996001960000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.228335</v>
+        <v>0.227087</v>
       </c>
       <c r="I2" t="n">
         <v>335153576</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.133031</v>
+        <v>9.714608999999999</v>
       </c>
       <c r="E3" t="n">
         <v>0.99980198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7395659999999999</v>
+        <v>0.739746</v>
       </c>
       <c r="G3" t="n">
         <v>0.998395485</v>
       </c>
       <c r="H3" t="n">
-        <v>0.223134</v>
+        <v>0.224865</v>
       </c>
       <c r="I3" t="n">
         <v>334662954.9999999</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.968598999999999</v>
+        <v>10.082349</v>
       </c>
       <c r="E4" t="n">
         <v>0.999982142</v>
       </c>
       <c r="F4" t="n">
-        <v>0.682075</v>
+        <v>0.652093</v>
       </c>
       <c r="G4" t="n">
         <v>0.976610349</v>
       </c>
       <c r="H4" t="n">
-        <v>0.251702</v>
+        <v>0.258115</v>
       </c>
       <c r="I4" t="n">
         <v>325792384</v>
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.256153</v>
+        <v>9.390421</v>
       </c>
       <c r="E5" t="n">
         <v>0.999985649</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6986059999999999</v>
+        <v>0.695796</v>
       </c>
       <c r="G5" t="n">
         <v>0.98701741</v>
       </c>
       <c r="H5" t="n">
-        <v>0.28718</v>
+        <v>0.283344</v>
       </c>
       <c r="I5" t="n">
         <v>330024049</v>

--- a/delays_zurich_transport_40753.xlsx
+++ b/delays_zurich_transport_40753.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.288106000000001</v>
+        <v>9.079942000000001</v>
       </c>
       <c r="E2" t="n">
         <v>0.999894722</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8115250000000001</v>
+        <v>0.734496</v>
       </c>
       <c r="G2" t="n">
         <v>0.9996001960000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.227087</v>
+        <v>0.222947</v>
       </c>
       <c r="I2" t="n">
         <v>335153576</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9.714608999999999</v>
+        <v>9.111621</v>
       </c>
       <c r="E3" t="n">
         <v>0.99980198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.739746</v>
+        <v>0.664442</v>
       </c>
       <c r="G3" t="n">
         <v>0.998395485</v>
       </c>
       <c r="H3" t="n">
-        <v>0.224865</v>
+        <v>0.22174</v>
       </c>
       <c r="I3" t="n">
         <v>334662954.9999999</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.082349</v>
+        <v>9.449009</v>
       </c>
       <c r="E4" t="n">
         <v>0.999982142</v>
       </c>
       <c r="F4" t="n">
-        <v>0.652093</v>
+        <v>0.663987</v>
       </c>
       <c r="G4" t="n">
         <v>0.976610349</v>
       </c>
       <c r="H4" t="n">
-        <v>0.258115</v>
+        <v>0.249104</v>
       </c>
       <c r="I4" t="n">
         <v>325792384</v>
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9.390421</v>
+        <v>9.743774</v>
       </c>
       <c r="E5" t="n">
         <v>0.999985649</v>
       </c>
       <c r="F5" t="n">
-        <v>0.695796</v>
+        <v>0.685737</v>
       </c>
       <c r="G5" t="n">
         <v>0.98701741</v>
       </c>
       <c r="H5" t="n">
-        <v>0.283344</v>
+        <v>0.283573</v>
       </c>
       <c r="I5" t="n">
         <v>330024049</v>
